--- a/output/pdf_financials_xlsx/PHA.xlsx
+++ b/output/pdf_financials_xlsx/PHA.xlsx
@@ -1487,18 +1487,16 @@
         <v>2.683483</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>5.12481</v>
+        <v>5.125</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.149</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.495</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>1.396</v>
       </c>
     </row>
     <row r="35">
@@ -1555,18 +1553,16 @@
         <v>2.683483</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>5.12481</v>
+        <v>5.125</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.149</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.495</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>1.396</v>
       </c>
     </row>
     <row r="37">
@@ -1961,13 +1957,13 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.51819</v>
+        <v>1.518</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.069</v>
+        <v>1.92</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.599</v>
+        <v>3.104</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -4961,7 +4957,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18551,7 +18547,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -20462,7 +20458,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -20980,7 +20976,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">

--- a/output/pdf_financials_xlsx/PHA.xlsx
+++ b/output/pdf_financials_xlsx/PHA.xlsx
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.581882</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>3.423</v>
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.52138</v>
+        <v>3.103262</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>4.664</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3.784216142500897</v>
+        <v>4.657534427499868</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>5.793285055957867</v>
@@ -3717,19 +3717,19 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.581882</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>3.422</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>4.449</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>6.812</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>8.206</v>
       </c>
     </row>
     <row r="101">
@@ -4101,19 +4101,19 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="113">
@@ -11295,7 +11295,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -11344,7 +11348,11 @@
           <t>Depreciation of right-of-use assets 11</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -11395,7 +11403,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12711,7 +12719,11 @@
           <t>Proceeds from disposal of property and equipment 8</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -13421,7 +13433,11 @@
           <t>Depreciation of property and equipment 11</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -13470,7 +13486,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -13521,7 +13541,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15039,7 +15059,11 @@
           <t>Depreciation of property and equipment 11</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -15086,7 +15110,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -15135,7 +15163,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -15186,7 +15214,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -15790,7 +15822,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PHA.xlsx
+++ b/output/pdf_financials_xlsx/PHA.xlsx
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.039171</v>
+        <v>1.496788</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-0.112</v>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.039171</v>
+        <v>1.496788</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-0.112</v>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>37.11325</v>
+        <v>53.456714</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1.559641019211225</v>
+        <v>2.246456032609774</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>-0.1391183375358664</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>1.039171</v>
+        <v>1.496788</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-0.112</v>
@@ -4229,19 +4229,19 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.073814</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.045</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-1.446</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-2.65</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-2.023</v>
       </c>
     </row>
     <row r="117">
@@ -4395,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.515</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -12515,7 +12515,11 @@
           <t>Acquisition of intangible assets 10</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -14204,7 +14208,11 @@
           <t>Acquisition of intangible assets 12</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -14708,7 +14716,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -16277,7 +16289,11 @@
           <t>Repurchase of shares 17</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -16483,7 +16499,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
